--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/CALIFORNIA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/CALIFORNIA_2017.xlsx
@@ -2317,7 +2317,7 @@
         <v>23</v>
       </c>
       <c r="D109">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="110">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C213">
@@ -4333,7 +4333,7 @@
         <v>23</v>
       </c>
       <c r="D221">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="222">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C269">
@@ -7285,7 +7285,7 @@
         <v>23</v>
       </c>
       <c r="D385">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="386">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C435">
@@ -10957,7 +10957,7 @@
         <v>23</v>
       </c>
       <c r="D589">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="590">
@@ -12073,7 +12073,7 @@
         <v>225</v>
       </c>
       <c r="D651">
-        <v>0.0009449414136323547</v>
+        <v>0.0009449414136323549</v>
       </c>
     </row>
     <row r="652">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C930">
@@ -19273,7 +19273,7 @@
         <v>23</v>
       </c>
       <c r="D1051">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1052">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1154">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1155">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1253">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1254">
@@ -23467,7 +23467,7 @@
         <v>236</v>
       </c>
       <c r="D1284">
-        <v>0.0009911385494099365</v>
+        <v>0.0009911385494099363</v>
       </c>
     </row>
     <row r="1285">
@@ -23647,7 +23647,7 @@
         <v>23</v>
       </c>
       <c r="D1294">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1295">
@@ -24133,7 +24133,7 @@
         <v>23</v>
       </c>
       <c r="D1321">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1322">
@@ -24241,7 +24241,7 @@
         <v>23</v>
       </c>
       <c r="D1327">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1328">
@@ -25159,7 +25159,7 @@
         <v>23</v>
       </c>
       <c r="D1378">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1379">
@@ -26203,7 +26203,7 @@
         <v>23</v>
       </c>
       <c r="D1436">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1437">
@@ -26268,7 +26268,7 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1440">
@@ -28669,7 +28669,7 @@
         <v>23</v>
       </c>
       <c r="D1573">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1574">
@@ -29389,7 +29389,7 @@
         <v>23</v>
       </c>
       <c r="D1613">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1614">
@@ -29479,7 +29479,7 @@
         <v>236</v>
       </c>
       <c r="D1618">
-        <v>0.0009911385494099365</v>
+        <v>0.0009911385494099363</v>
       </c>
     </row>
     <row r="1619">
@@ -29605,7 +29605,7 @@
         <v>23</v>
       </c>
       <c r="D1625">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1626">
@@ -30073,7 +30073,7 @@
         <v>23</v>
       </c>
       <c r="D1651">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1652">
@@ -30397,7 +30397,7 @@
         <v>23</v>
       </c>
       <c r="D1669">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1670">
@@ -30973,7 +30973,7 @@
         <v>23</v>
       </c>
       <c r="D1701">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1702">
@@ -31099,7 +31099,7 @@
         <v>23</v>
       </c>
       <c r="D1708">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1709">
@@ -35682,7 +35682,7 @@
       </c>
       <c r="B1963" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1963">
@@ -35941,7 +35941,7 @@
         <v>23</v>
       </c>
       <c r="D1977">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="1978">
@@ -36391,7 +36391,7 @@
         <v>23</v>
       </c>
       <c r="D2002">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="2003">
@@ -36877,7 +36877,7 @@
         <v>23</v>
       </c>
       <c r="D2029">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="2030">
@@ -37255,7 +37255,7 @@
         <v>23</v>
       </c>
       <c r="D2050">
-        <v>9.659401117130737E-05</v>
+        <v>9.659401117130736E-05</v>
       </c>
     </row>
     <row r="2051">
